--- a/excel/mafe_to_poe_conversions_for_psha.xlsx
+++ b/excel/mafe_to_poe_conversions_for_psha.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\clemettn\Documents\phd\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E9F7F33-43F2-4C3D-A059-65B82EC6DB10}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{233AEA56-1747-412B-9F90-AD04CB7C4B0B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="360" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
@@ -70,7 +70,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="165" formatCode="0.000000"/>
+    <numFmt numFmtId="164" formatCode="0.000000"/>
   </numFmts>
   <fonts count="5" x14ac:knownFonts="1">
     <font>
@@ -138,7 +138,7 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
@@ -419,7 +419,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B2:D10"/>
+  <dimension ref="B2:D13"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="11.42578125" bestFit="1" customWidth="1"/>
@@ -463,15 +463,15 @@
     </row>
     <row r="5" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B5" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="C5" s="4">
         <f t="shared" ref="C5:C10" si="0">1/B5</f>
-        <v>0.01</v>
+        <v>5.0000000000000001E-3</v>
       </c>
       <c r="D5" s="5">
         <f t="shared" ref="D5:D10" si="1">ROUND(1-EXP(-C5*$C$2), 6)</f>
-        <v>9.9500000000000005E-3</v>
+        <v>4.9880000000000002E-3</v>
       </c>
     </row>
     <row r="6" spans="2:4" x14ac:dyDescent="0.25">
@@ -537,6 +537,11 @@
       <c r="D10" s="5">
         <f t="shared" si="1"/>
         <v>1E-4</v>
+      </c>
+    </row>
+    <row r="13" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="D13">
+        <v>4.9880000000000002E-3</v>
       </c>
     </row>
   </sheetData>
